--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_49.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_9_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4645870.139794774</v>
+        <v>4682248.623417665</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13279501.51514059</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13279501.51514059</v>
+        <v>13275569.19337385</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>987.0883260128553</v>
+        <v>603.5370117102299</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>987.0883260128553</v>
+        <v>603.5370117102299</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18805689.90910076</v>
+        <v>18806456.82317137</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>1.415908396047982</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H2" t="n">
-        <v>3.769060713577687</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.41253966162023</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,28 +778,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>338.7548582517823</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>180.4207859386202</v>
       </c>
       <c r="X3" t="n">
-        <v>373</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N4" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O4" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P4" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.343301935257443</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>3.769060713577687</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I5" t="n">
-        <v>1.953406460791434</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.41253966161941</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,28 +1015,28 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>62.44885845517734</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
-        <v>4.464774651476091</v>
+        <v>129.3917660166838</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V6" t="n">
         <v>374</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
-        <v>351.4836353066767</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N7" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O7" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P7" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.343301935257443</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577687</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.36594612241093</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8805867536895</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1884925285102</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1219,13 +1219,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>42.83283561629863</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018132</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S9" t="n">
-        <v>62.44885845517734</v>
+        <v>374</v>
       </c>
       <c r="T9" t="n">
-        <v>4.464774651476091</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>374</v>
       </c>
       <c r="X9" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>128.5934283178948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.51638189435317</v>
+        <v>91.79905402550071</v>
       </c>
       <c r="N10" t="n">
-        <v>142.7621408454554</v>
+        <v>143.0380916651276</v>
       </c>
       <c r="O10" t="n">
-        <v>214.1923837511461</v>
+        <v>214.4472689970478</v>
       </c>
       <c r="P10" t="n">
-        <v>264.9837661807364</v>
+        <v>265.2018645413922</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.286266425598</v>
+        <v>310.437266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.2506853582003</v>
+        <v>318.3317673254134</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>26.93768689770263</v>
@@ -1456,10 +1456,10 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>113.5995101105027</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>324.9996113467254</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
         <v>4.021973978873973</v>
@@ -1495,7 +1495,7 @@
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
@@ -1507,13 +1507,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>78.39139276613435</v>
+        <v>173.3546605387599</v>
       </c>
     </row>
     <row r="13">
@@ -1553,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N13" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O13" t="n">
         <v>231.765039488851</v>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63.55655664632661</v>
+        <v>158.5198244189524</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>3.99961134672543</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
         <v>180.333570877285</v>
@@ -1738,10 +1738,10 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>252.7534963968768</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
         <v>111.3731429098285</v>
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1933,13 +1933,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>306.9405130354634</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H18" t="n">
-        <v>325.021973978874</v>
+        <v>98.98524175149993</v>
       </c>
       <c r="I18" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1963,16 +1963,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
         <v>501.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T18" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U18" t="n">
         <v>79.16168051490371</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,13 +2091,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H20" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4605873653143577</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2158,22 +2158,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>213.6917283274922</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,25 +2206,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V21" t="n">
-        <v>93.51066719152016</v>
+        <v>267.1024830734933</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2398,19 +2398,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>195.2639131038857</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2443,13 +2443,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
@@ -2458,10 +2458,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2568,10 +2568,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2629,16 +2629,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>26.93768689770263</v>
+        <v>121.9009546703284</v>
       </c>
       <c r="E27" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
@@ -2647,10 +2647,10 @@
         <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
-        <v>306.962875667612</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
         <v>180.333570877285</v>
@@ -2692,7 +2692,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>98.86273944538755</v>
@@ -2741,10 +2741,10 @@
         <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N28" t="n">
-        <v>154.4197474548741</v>
+        <v>155.2579933044718</v>
       </c>
       <c r="O28" t="n">
         <v>231.765039488851</v>
@@ -2802,7 +2802,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
         <v>72.84688483418068</v>
@@ -2872,7 +2872,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>251.250040477093</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -2881,13 +2881,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,16 +2914,16 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
-        <v>275.2968386499106</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2987,16 +2987,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>376.8716854102422</v>
       </c>
       <c r="S31" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>135.063180218145</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.999611346725456</v>
@@ -3154,7 +3154,7 @@
         <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
@@ -3163,7 +3163,7 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
         <v>111.3731429098285</v>
@@ -3172,7 +3172,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>173.3546605387602</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="34">
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M34" t="n">
         <v>102.3923982877958</v>
@@ -3233,7 +3233,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H35" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3355,10 +3355,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H36" t="n">
-        <v>98.98524175149967</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3391,22 +3391,22 @@
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V36" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>193.8260072180132</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q37" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S37" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3516,10 +3516,10 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H38" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3583,19 +3583,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H39" t="n">
-        <v>98.98524175149964</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3637,16 +3637,16 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>98.86273944538755</v>
+        <v>193.8260072180132</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3750,10 +3750,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,25 +3814,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3865,13 +3865,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>252.7534963968768</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
@@ -3880,10 +3880,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598396</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T44" t="n">
         <v>259.6218731858503</v>
@@ -4057,7 +4057,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
@@ -4066,10 +4066,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608471</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,25 +4099,25 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>252.7534963968771</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V45" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>78.39139276613435</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.8416377852019</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C2" t="n">
-        <v>54.86731632763228</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D2" t="n">
-        <v>44.42372467121835</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E2" t="n">
-        <v>40.01636143195709</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F2" t="n">
-        <v>35.07734253497542</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
-        <v>33.64713203391685</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>399.11</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>451.2545884924623</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>515.9445614572863</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M2" t="n">
-        <v>885.2145614572864</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>1064.065793611129</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1064.065793611129</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1122.73</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1405.724707412505</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1218.99441573196</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U2" t="n">
-        <v>967.2891925799697</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V2" t="n">
-        <v>735.1164408963092</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W2" t="n">
-        <v>494.3351520266652</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X2" t="n">
-        <v>300.1110778239705</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y2" t="n">
-        <v>187.6692266292166</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>381.2922089875784</v>
+        <v>926.4447280102922</v>
       </c>
       <c r="C3" t="n">
-        <v>381.2922089875784</v>
+        <v>926.4447280102922</v>
       </c>
       <c r="D3" t="n">
-        <v>29.84</v>
+        <v>574.9925190227137</v>
       </c>
       <c r="E3" t="n">
-        <v>29.84</v>
+        <v>574.9925190227137</v>
       </c>
       <c r="F3" t="n">
-        <v>29.84</v>
+        <v>574.9925190227137</v>
       </c>
       <c r="G3" t="n">
-        <v>29.84</v>
+        <v>574.9925190227137</v>
       </c>
       <c r="H3" t="n">
-        <v>29.84</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I3" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="J3" t="n">
-        <v>174.5185557413367</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K3" t="n">
-        <v>399.1286311753428</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L3" t="n">
-        <v>714.3818833454036</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M3" t="n">
-        <v>856.0360750882628</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N3" t="n">
-        <v>1046.360878846775</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1337.587921002191</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P3" t="n">
-        <v>1492</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1345.738421006376</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R3" t="n">
-        <v>1210.871311105555</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S3" t="n">
-        <v>1147.791656100326</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T3" t="n">
-        <v>805.6150316035757</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U3" t="n">
-        <v>805.4172696960114</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V3" t="n">
-        <v>790.7600301086173</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W3" t="n">
-        <v>758.0598857552552</v>
+        <v>946.5081011874514</v>
       </c>
       <c r="X3" t="n">
-        <v>381.2922089875784</v>
+        <v>926.4447280102922</v>
       </c>
       <c r="Y3" t="n">
-        <v>381.2922089875784</v>
+        <v>926.4447280102922</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>738.8440414227464</v>
+        <v>927.7465538602398</v>
       </c>
       <c r="C4" t="n">
-        <v>738.8440414227464</v>
+        <v>1053.748559678676</v>
       </c>
       <c r="D4" t="n">
-        <v>852.1631855477465</v>
+        <v>1053.748559678676</v>
       </c>
       <c r="E4" t="n">
-        <v>969.9920897591595</v>
+        <v>1171.577463890088</v>
       </c>
       <c r="F4" t="n">
-        <v>1094.353062351095</v>
+        <v>1171.577463890088</v>
       </c>
       <c r="G4" t="n">
-        <v>1094.353062351095</v>
+        <v>1171.577463890088</v>
       </c>
       <c r="H4" t="n">
-        <v>1094.353062351095</v>
+        <v>1171.577463890088</v>
       </c>
       <c r="I4" t="n">
-        <v>1094.353062351095</v>
+        <v>1171.577463890088</v>
       </c>
       <c r="J4" t="n">
-        <v>1253.659110653045</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K4" t="n">
-        <v>1385.387095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
-        <v>1385.387095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1292.946305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1148.742122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>932.3861797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>664.7258098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.3053387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.29478771712391</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>70.29478771712391</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>316.8560101914761</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V4" t="n">
-        <v>515.677403077422</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W4" t="n">
-        <v>515.677403077422</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="X4" t="n">
-        <v>515.677403077422</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="Y4" t="n">
-        <v>627.0867037564543</v>
+        <v>815.9892161939478</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.8416377852028</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>58.86731632763319</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>48.42372467121926</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>44.016361431958</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>39.07734253497633</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>35.70026987310013</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>31.89313783918327</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>30.01969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.2796902997726</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>464.9696632645968</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>835.2296632645968</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1205.489663264597</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O5" t="n">
-        <v>1205.489663264597</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P5" t="n">
-        <v>1264.153869653468</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.724707412506</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.994415731961</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>971.2891925799706</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>739.1164408963101</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>498.3351520266661</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>304.1110778239714</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.6692266292175</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>381.3722089875785</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="C6" t="n">
-        <v>381.3722089875785</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.5985557413367</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K6" t="n">
-        <v>399.2086311753428</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L6" t="n">
-        <v>718.1819687139391</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M6" t="n">
-        <v>859.8361604567983</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N6" t="n">
-        <v>1050.16096421531</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1341.388006370727</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P6" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1349.538506374912</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1214.671396474091</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>1151.591741468861</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>1147.081868083532</v>
+        <v>1017.426340959346</v>
       </c>
       <c r="U6" t="n">
-        <v>1146.884106175968</v>
+        <v>1017.22843611296</v>
       </c>
       <c r="V6" t="n">
-        <v>769.1063283981898</v>
+        <v>639.4506583351822</v>
       </c>
       <c r="W6" t="n">
-        <v>736.4061840448277</v>
+        <v>261.6728805574044</v>
       </c>
       <c r="X6" t="n">
-        <v>381.3722089875785</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="Y6" t="n">
-        <v>381.3722089875785</v>
+        <v>241.6095073802453</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216.7976894066533</v>
+        <v>793.7055332299248</v>
       </c>
       <c r="C7" t="n">
-        <v>342.7996952250891</v>
+        <v>793.7055332299248</v>
       </c>
       <c r="D7" t="n">
-        <v>456.1188393500892</v>
+        <v>907.0246773549248</v>
       </c>
       <c r="E7" t="n">
-        <v>573.9477435615022</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="F7" t="n">
-        <v>698.3087161534377</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="G7" t="n">
-        <v>851.8991623681918</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="H7" t="n">
-        <v>1023.050610806278</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I7" t="n">
-        <v>1249.71327269318</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J7" t="n">
-        <v>1249.71327269318</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K7" t="n">
-        <v>1381.441257449721</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M7" t="n">
-        <v>1293.026305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N7" t="n">
-        <v>1148.822122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O7" t="n">
-        <v>932.4661797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P7" t="n">
-        <v>664.8058098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.3853387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.37478771712392</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>70.37478771712392</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U7" t="n">
-        <v>70.37478771712392</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V7" t="n">
-        <v>70.37478771712392</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W7" t="n">
-        <v>70.37478771712392</v>
+        <v>793.7055332299248</v>
       </c>
       <c r="X7" t="n">
-        <v>70.37478771712392</v>
+        <v>793.7055332299248</v>
       </c>
       <c r="Y7" t="n">
-        <v>105.0403517403612</v>
+        <v>793.7055332299248</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.8684999460195</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C8" t="n">
-        <v>56.89417848844992</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D8" t="n">
-        <v>46.450586832036</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E8" t="n">
-        <v>42.04322359277474</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F8" t="n">
-        <v>37.10420469579307</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391686</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4798,22 +4798,22 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>452.3245884924623</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>517.0145614572864</v>
+        <v>834.5019149748742</v>
       </c>
       <c r="M8" t="n">
-        <v>887.2745614572864</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.751569573322</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.021277892777</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3160547407873</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1433030571268</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W8" t="n">
-        <v>496.3620141874828</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1379399847881</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6960887900342</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>416.2524019739147</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>416.2524019739147</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>416.2524019739147</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>416.2524019739147</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>73.18549052151377</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>73.18549052151377</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.5985557413367</v>
+        <v>174.3973709300159</v>
       </c>
       <c r="K9" t="n">
-        <v>399.2086311753428</v>
+        <v>398.6635894772295</v>
       </c>
       <c r="L9" t="n">
-        <v>718.1819687139391</v>
+        <v>717.174568996958</v>
       </c>
       <c r="M9" t="n">
-        <v>859.8361604567983</v>
+        <v>858.2892107398172</v>
       </c>
       <c r="N9" t="n">
-        <v>1050.16096421531</v>
+        <v>1048.06018421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1341.388006370727</v>
+        <v>1338.780579861293</v>
       </c>
       <c r="P9" t="n">
-        <v>1495.800085368536</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1495.800085368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1360.932975467714</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1297.853320462485</v>
+        <v>833.4673281331341</v>
       </c>
       <c r="T9" t="n">
-        <v>1293.343447077155</v>
+        <v>828.9486973626322</v>
       </c>
       <c r="U9" t="n">
-        <v>1293.145685169591</v>
+        <v>828.7507925162457</v>
       </c>
       <c r="V9" t="n">
-        <v>915.3679073918131</v>
+        <v>814.0935529288516</v>
       </c>
       <c r="W9" t="n">
-        <v>537.5901296140353</v>
+        <v>436.3157751510738</v>
       </c>
       <c r="X9" t="n">
-        <v>159.8123518362574</v>
+        <v>416.2524019739147</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>416.2524019739147</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1250.707100357225</v>
+        <v>576.0083476291953</v>
       </c>
       <c r="C10" t="n">
-        <v>1376.709106175661</v>
+        <v>702.0103534476311</v>
       </c>
       <c r="D10" t="n">
-        <v>1385.467095409585</v>
+        <v>815.3294975726312</v>
       </c>
       <c r="E10" t="n">
-        <v>1385.467095409585</v>
+        <v>933.1584017840443</v>
       </c>
       <c r="F10" t="n">
-        <v>1385.467095409585</v>
+        <v>1057.51937437598</v>
       </c>
       <c r="G10" t="n">
-        <v>1385.467095409585</v>
+        <v>1211.108035344832</v>
       </c>
       <c r="H10" t="n">
-        <v>1385.467095409585</v>
+        <v>1382.243611323902</v>
       </c>
       <c r="I10" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J10" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
-        <v>1385.467095409585</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M10" t="n">
-        <v>1293.026305617309</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N10" t="n">
-        <v>1148.822122945132</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O10" t="n">
-        <v>932.4661797621563</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P10" t="n">
-        <v>664.8058098826245</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.3853387456568</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.37478771712392</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>505.7973598420842</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>704.6187527280301</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>876.5096709877075</v>
+        <v>201.8109182596774</v>
       </c>
       <c r="X10" t="n">
-        <v>1027.540462011901</v>
+        <v>352.841709283871</v>
       </c>
       <c r="Y10" t="n">
-        <v>1138.949762690933</v>
+        <v>464.2510099629032</v>
       </c>
     </row>
     <row r="11">
@@ -5008,49 +5008,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C11" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D11" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E11" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F11" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L11" t="n">
-        <v>1844.448527309012</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M11" t="n">
-        <v>1844.448527309012</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N11" t="n">
-        <v>1844.448527309012</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>2005.578628691967</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
-        <v>2202.170635030587</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
@@ -5065,19 +5065,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="12">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>588.6177696982188</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C12" t="n">
-        <v>548.1128076320377</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D12" t="n">
-        <v>520.9030228868836</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E12" t="n">
-        <v>499.0120155920224</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
-        <v>384.2650356824237</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
         <v>55.98259997866058</v>
@@ -5138,25 +5138,25 @@
         <v>1982.60944240224</v>
       </c>
       <c r="S12" t="n">
-        <v>1525.215274341931</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T12" t="n">
-        <v>1443.01795098519</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U12" t="n">
-        <v>1363.056657535792</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V12" t="n">
-        <v>1268.601438150418</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W12" t="n">
-        <v>831.8608897566517</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X12" t="n">
-        <v>731.9995367815127</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y12" t="n">
-        <v>652.8163117652153</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="13">
@@ -5196,10 +5196,10 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
         <v>1349.248439584877</v>
@@ -5269,22 +5269,22 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L14" t="n">
-        <v>991.9887866314309</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M14" t="n">
-        <v>1009.32297330616</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N14" t="n">
-        <v>1651.83297330616</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="O14" t="n">
-        <v>1812.963074689115</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="P14" t="n">
         <v>2009.555081027735</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>816.937701241021</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C15" t="n">
         <v>776.43273917484</v>
       </c>
       <c r="D15" t="n">
-        <v>749.2229544296858</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
         <v>60.0226114399994</v>
@@ -5369,31 +5369,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R15" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S15" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U15" t="n">
-        <v>1591.376589078594</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V15" t="n">
-        <v>1172.678945450796</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W15" t="n">
-        <v>1060.180821299454</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X15" t="n">
-        <v>960.3194683243149</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y15" t="n">
-        <v>881.1362433080176</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="16">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C17" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D17" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E17" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F17" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G17" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L17" t="n">
-        <v>523.631587033441</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="M17" t="n">
-        <v>1166.141587033441</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="N17" t="n">
-        <v>1170.453074689115</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O17" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P17" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X17" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>992.2829698086708</v>
+        <v>264.3753454557947</v>
       </c>
       <c r="C18" t="n">
-        <v>951.7780077424898</v>
+        <v>223.8703833896136</v>
       </c>
       <c r="D18" t="n">
-        <v>924.5682229973356</v>
+        <v>196.6605986444594</v>
       </c>
       <c r="E18" t="n">
-        <v>902.6772157024744</v>
+        <v>174.7695913495982</v>
       </c>
       <c r="F18" t="n">
-        <v>883.8527284924978</v>
+        <v>155.9451041396216</v>
       </c>
       <c r="G18" t="n">
-        <v>573.8118062344539</v>
+        <v>151.9050926782828</v>
       </c>
       <c r="H18" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I18" t="n">
         <v>51.92</v>
@@ -5606,31 +5606,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R18" t="n">
-        <v>1737.789794027844</v>
+        <v>1658.367018159816</v>
       </c>
       <c r="S18" t="n">
-        <v>1604.638050209959</v>
+        <v>1200.972850099507</v>
       </c>
       <c r="T18" t="n">
-        <v>1522.440726853217</v>
+        <v>794.5331025003411</v>
       </c>
       <c r="U18" t="n">
-        <v>1442.479433403819</v>
+        <v>714.5718090509434</v>
       </c>
       <c r="V18" t="n">
-        <v>1348.024214018445</v>
+        <v>620.1165896655696</v>
       </c>
       <c r="W18" t="n">
-        <v>1235.526089867104</v>
+        <v>507.6184655142276</v>
       </c>
       <c r="X18" t="n">
-        <v>1135.664736891965</v>
+        <v>407.7571125390887</v>
       </c>
       <c r="Y18" t="n">
-        <v>1056.481511875667</v>
+        <v>328.5738875227913</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,49 +5719,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C20" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D20" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F20" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G20" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H20" t="n">
-        <v>52.3852397629438</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>949.6332762537361</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M20" t="n">
-        <v>949.6332762537362</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N20" t="n">
-        <v>1170.453074689115</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O20" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P20" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5779,16 +5779,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W20" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1316.525394051095</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D21" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E21" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F21" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5852,22 +5852,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U21" t="n">
         <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W21" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X21" t="n">
-        <v>1459.907161134389</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y21" t="n">
-        <v>1380.723936118091</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="22">
@@ -5919,13 +5919,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5983,13 +5983,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L23" t="n">
-        <v>523.631587033441</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="M23" t="n">
-        <v>563.4049796447796</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N23" t="n">
         <v>1205.91497964478</v>
@@ -6004,28 +6004,28 @@
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>992.2829698086707</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C24" t="n">
-        <v>627.5355835000653</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D24" t="n">
-        <v>276.0833745124868</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E24" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F24" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6089,7 +6089,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U24" t="n">
         <v>1766.721857646244</v>
@@ -6101,10 +6101,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y24" t="n">
-        <v>1380.723936118092</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6211,7 +6211,7 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H26" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
@@ -6220,13 +6220,13 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>733.5813277110226</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L26" t="n">
-        <v>949.6332762537361</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M26" t="n">
-        <v>1009.32297330616</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N26" t="n">
         <v>1651.83297330616</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>992.2829698086708</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C27" t="n">
-        <v>951.7780077424898</v>
+        <v>872.355231874462</v>
       </c>
       <c r="D27" t="n">
-        <v>924.5682229973356</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E27" t="n">
-        <v>902.6772157024744</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F27" t="n">
-        <v>559.6103042500736</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G27" t="n">
-        <v>555.5702927887347</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H27" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6317,31 +6317,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R27" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S27" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V27" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W27" t="n">
-        <v>1235.526089867104</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X27" t="n">
-        <v>1135.664736891965</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y27" t="n">
-        <v>1056.481511875667</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="28">
@@ -6384,7 +6384,7 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N28" t="n">
         <v>1349.248439584877</v>
@@ -6442,7 +6442,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G29" t="n">
         <v>125.5027119537179</v>
@@ -6454,19 +6454,19 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L29" t="n">
-        <v>523.631587033441</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="M29" t="n">
-        <v>527.9430746891146</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N29" t="n">
-        <v>1170.453074689115</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O29" t="n">
         <v>1812.963074689115</v>
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1141.180125483445</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C30" t="n">
-        <v>1100.675163417264</v>
+        <v>1196.597656116886</v>
       </c>
       <c r="D30" t="n">
-        <v>749.2229544296858</v>
+        <v>942.8097364430548</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0895228924003</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H30" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I30" t="n">
         <v>51.92</v>
@@ -6557,28 +6557,28 @@
         <v>2164.764564500508</v>
       </c>
       <c r="R30" t="n">
-        <v>1886.686949702618</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S30" t="n">
-        <v>1753.535205884734</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T30" t="n">
-        <v>1671.337882527992</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U30" t="n">
-        <v>1591.376589078594</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V30" t="n">
-        <v>1496.92136969322</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W30" t="n">
-        <v>1384.423245541878</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X30" t="n">
-        <v>1284.561892566739</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y30" t="n">
-        <v>1205.378667550442</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="31">
@@ -6630,13 +6630,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R31" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6694,49 +6694,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L32" t="n">
-        <v>950.0896384907273</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M32" t="n">
-        <v>1592.599638490728</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N32" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O32" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P32" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.4528527561725</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C33" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D33" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E33" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F33" t="n">
         <v>60.02261143999941</v>
@@ -6797,25 +6797,25 @@
         <v>1982.60944240224</v>
       </c>
       <c r="S33" t="n">
-        <v>1525.215274341931</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T33" t="n">
-        <v>1443.01795098519</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U33" t="n">
-        <v>1363.056657535792</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V33" t="n">
-        <v>944.3590139079936</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W33" t="n">
-        <v>831.8608897566517</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X33" t="n">
-        <v>731.9995367815127</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y33" t="n">
-        <v>556.8938190655933</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="34">
@@ -6855,25 +6855,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L34" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M34" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N34" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O34" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R34" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D35" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H35" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
@@ -6931,49 +6931,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L35" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M35" t="n">
-        <v>1756.89799366138</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N35" t="n">
-        <v>1756.89799366138</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O35" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P35" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W35" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>264.3753454557945</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C36" t="n">
-        <v>223.8703833896134</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D36" t="n">
-        <v>196.6605986444592</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E36" t="n">
-        <v>174.769591349598</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F36" t="n">
-        <v>155.9451041396213</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G36" t="n">
-        <v>151.9050926782825</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7034,13 +7034,13 @@
         <v>1982.60944240224</v>
       </c>
       <c r="S36" t="n">
-        <v>1525.215274341931</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T36" t="n">
-        <v>1443.01795098519</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U36" t="n">
-        <v>1363.056657535792</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V36" t="n">
         <v>1268.601438150418</v>
@@ -7049,10 +7049,10 @@
         <v>831.8608897566517</v>
       </c>
       <c r="X36" t="n">
-        <v>407.7571125390884</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y36" t="n">
-        <v>328.5738875227911</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="37">
@@ -7104,13 +7104,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q37" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R37" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7159,31 +7159,31 @@
         <v>125.9679517166614</v>
       </c>
       <c r="H38" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I38" t="n">
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L38" t="n">
-        <v>523.631587033441</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M38" t="n">
-        <v>1166.141587033441</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N38" t="n">
-        <v>1808.651587033441</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O38" t="n">
-        <v>1969.781688416396</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P38" t="n">
-        <v>2166.373694755016</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1237.102618183067</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C39" t="n">
-        <v>1196.597656116886</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D39" t="n">
-        <v>845.1454471293077</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E39" t="n">
-        <v>499.0120155920222</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F39" t="n">
-        <v>155.9451041396213</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G39" t="n">
-        <v>151.9050926782825</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7280,16 +7280,16 @@
         <v>1687.299081778216</v>
       </c>
       <c r="V39" t="n">
-        <v>1592.843862392842</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W39" t="n">
-        <v>1480.3457382415</v>
+        <v>831.8608897566517</v>
       </c>
       <c r="X39" t="n">
-        <v>1380.484385266361</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y39" t="n">
-        <v>1301.301160250064</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="40">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7405,19 +7405,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>523.631587033441</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M41" t="n">
-        <v>523.631587033441</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N41" t="n">
-        <v>724.5350810277346</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O41" t="n">
-        <v>1367.045081027735</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P41" t="n">
         <v>2009.555081027735</v>
@@ -7426,28 +7426,28 @@
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>492.6952769985968</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C42" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D42" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E42" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7511,22 +7511,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U42" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V42" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W42" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X42" t="n">
-        <v>960.3194683243149</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y42" t="n">
-        <v>556.8938190655933</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="43">
@@ -7578,13 +7578,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7627,7 +7627,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G44" t="n">
         <v>125.5027119537179</v>
@@ -7639,31 +7639,31 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>949.6332762537361</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M44" t="n">
-        <v>949.6332762537362</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N44" t="n">
-        <v>1170.453074689115</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O44" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P44" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S44" t="n">
         <v>2451.762030971221</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>168.4528527561725</v>
+        <v>668.0405455662465</v>
       </c>
       <c r="C45" t="n">
-        <v>127.9478906899915</v>
+        <v>627.5355835000654</v>
       </c>
       <c r="D45" t="n">
-        <v>100.7381059448373</v>
+        <v>276.083374512487</v>
       </c>
       <c r="E45" t="n">
-        <v>78.84709864997603</v>
+        <v>254.1923672176257</v>
       </c>
       <c r="F45" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076491</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463102</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7742,28 +7742,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1280.395625967535</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>873.9558783683688</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U45" t="n">
-        <v>618.6493163513212</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V45" t="n">
-        <v>524.1940969659473</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W45" t="n">
-        <v>411.6959728146054</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X45" t="n">
-        <v>311.8346198394665</v>
+        <v>811.4223126495403</v>
       </c>
       <c r="Y45" t="n">
-        <v>232.6513948231691</v>
+        <v>732.239087633243</v>
       </c>
     </row>
     <row r="46">
@@ -7803,25 +7803,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>372.8993027275024</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="M2" t="n">
-        <v>844.554996989051</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>584.0231602860407</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4816735941929551</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>501.1077446289929</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>384.3316744713784</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>321.3286984924623</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>845.554996989051</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>777.3653500296342</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4816735941929551</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>362.2957550800353</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>373.8993027275024</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>845.554996989051</v>
+        <v>707.7620966723902</v>
       </c>
       <c r="N8" t="n">
-        <v>584.9827562456367</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4816735941929551</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.1077446289929</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L11" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>421.2909076101267</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,25 +8912,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>318.9437086192779</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>223.0503014498774</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>342.3308260703579</v>
       </c>
       <c r="M17" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N17" t="n">
-        <v>234.8470915832563</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>486.2423218353989</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M20" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>453.5423549970993</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O20" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>216.0870636498471</v>
       </c>
       <c r="M23" t="n">
-        <v>341.6095732017122</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9863,16 +9863,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>361.7270524351312</v>
+        <v>537.6389720331213</v>
       </c>
       <c r="N26" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10097,22 +10097,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>236.2045428832664</v>
       </c>
       <c r="M29" t="n">
-        <v>305.789467185889</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N29" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O29" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L32" t="n">
         <v>430.7657085427136</v>
@@ -10346,7 +10346,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>290.3237048759414</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>643.3042832636559</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>230.4920535472222</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O35" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>537.6389720331213</v>
       </c>
       <c r="N38" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>457.4494331410071</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,22 +11048,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M41" t="n">
-        <v>301.434429149855</v>
+        <v>537.1780000765643</v>
       </c>
       <c r="N41" t="n">
-        <v>433.4248757636803</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O41" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>301.434429149855</v>
+        <v>911.3123136417682</v>
       </c>
       <c r="N44" t="n">
-        <v>453.5423549970993</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O44" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.927393539209461</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23411,13 +23411,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24599,10 +24599,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8382458495976266</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -24851,10 +24851,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25322,13 +25322,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25799,10 +25799,10 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>734487.1092780825</v>
+        <v>734756.8010130918</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1395766.8199117</v>
+        <v>1395929.747187704</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2056939.766086313</v>
+        <v>2057102.693362317</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2717750.208863221</v>
+        <v>2717830.754639224</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3378912.593140129</v>
+        <v>3378993.138916132</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4040074.977417035</v>
+        <v>4040155.523193039</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4701237.36169394</v>
+        <v>4701317.907469943</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5362399.745970844</v>
+        <v>5362480.291746847</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6023562.130247748</v>
+        <v>6023642.676023752</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6684724.514524654</v>
+        <v>6684805.060300657</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7345886.898801563</v>
+        <v>7345967.444577566</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8007049.283078476</v>
+        <v>8007129.828854479</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8668211.667355388</v>
+        <v>8668292.213131392</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9329374.0516323</v>
+        <v>9329454.597408304</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9990536.435909213</v>
+        <v>9990616.981685216</v>
       </c>
     </row>
   </sheetData>
@@ -26269,34 +26269,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1542548.934263421</v>
+        <v>1542736.874407429</v>
       </c>
       <c r="C2" t="n">
         <v>1542736.874407429</v>
       </c>
       <c r="D2" t="n">
-        <v>1542736.874407428</v>
+        <v>1542736.874407429</v>
       </c>
       <c r="E2" t="n">
-        <v>1542712.22997945</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="F2" t="n">
         <v>1542712.229979451</v>
       </c>
       <c r="G2" t="n">
-        <v>1542712.229979451</v>
+        <v>1542712.22997945</v>
       </c>
       <c r="H2" t="n">
         <v>1542712.229979451</v>
       </c>
       <c r="I2" t="n">
-        <v>1542712.229979452</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="J2" t="n">
         <v>1542712.229979451</v>
       </c>
       <c r="K2" t="n">
-        <v>1542712.22997945</v>
+        <v>1542712.229979452</v>
       </c>
       <c r="L2" t="n">
         <v>1542712.229979451</v>
@@ -26305,10 +26305,10 @@
         <v>1542712.229979451</v>
       </c>
       <c r="N2" t="n">
-        <v>1542712.229979452</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="O2" t="n">
-        <v>1542712.229979452</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="P2" t="n">
         <v>1542712.229979451</v>
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231721</v>
+        <v>231098</v>
       </c>
       <c r="C3" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>588575</v>
+        <v>589550</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388096</v>
+        <v>388448</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577307.7597977305</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575232.189518024</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573221.1009892204</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216768</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58551.39999999999</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58612.2</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>58612.2</v>
+        <v>58590.39999999999</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>674968.77446569</v>
+        <v>682084.9046736411</v>
       </c>
       <c r="C6" t="n">
-        <v>908540.4848894048</v>
+        <v>915191.8268611297</v>
       </c>
       <c r="D6" t="n">
-        <v>910903.5734182079</v>
+        <v>917203.4742769535</v>
       </c>
       <c r="E6" t="n">
-        <v>390253.7011832754</v>
+        <v>395741.6923136299</v>
       </c>
       <c r="F6" t="n">
-        <v>980514.7640014986</v>
+        <v>986977.7551318529</v>
       </c>
       <c r="G6" t="n">
-        <v>982203.1535231514</v>
+        <v>988666.1446535053</v>
       </c>
       <c r="H6" t="n">
-        <v>983893.8864331142</v>
+        <v>990356.8775634692</v>
       </c>
       <c r="I6" t="n">
-        <v>985586.9796336625</v>
+        <v>992049.9707640159</v>
       </c>
       <c r="J6" t="n">
-        <v>599186.4502485868</v>
+        <v>605297.4413789408</v>
       </c>
       <c r="K6" t="n">
-        <v>988628.3156274193</v>
+        <v>995443.3067577748</v>
       </c>
       <c r="L6" t="n">
-        <v>990680.593349764</v>
+        <v>997143.5844801186</v>
       </c>
       <c r="M6" t="n">
-        <v>895583.301229732</v>
+        <v>902046.2923600858</v>
       </c>
       <c r="N6" t="n">
-        <v>994088.4573204961</v>
+        <v>1000551.44845085</v>
       </c>
       <c r="O6" t="n">
-        <v>738996.0799189581</v>
+        <v>745459.0710493114</v>
       </c>
       <c r="P6" t="n">
-        <v>997506.1875705408</v>
+        <v>1003969.178700896</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -27002,13 +27002,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>-0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,13 +27100,13 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.1177124465037</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>224.8682520946261</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>399.9999999999992</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>65.70991639969378</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27575,10 +27575,10 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
+        <v>251.9523569712083</v>
+      </c>
+      <c r="X3" t="n">
         <v>400</v>
-      </c>
-      <c r="X3" t="n">
-        <v>46.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27594,34 +27594,34 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.858135136612</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
-        <v>171.047816275856</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>183.0524934032025</v>
+        <v>239.6042642698033</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
-        <v>395.9334970102382</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,7 +27645,7 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2309599488807</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I5" t="n">
-        <v>132.1643059857123</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>224.8682520946261</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,13 +27764,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.517988705216</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0284079411381</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>275.0816784461131</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>40.51066719152016</v>
       </c>
       <c r="W6" t="n">
+        <v>58.37314290982852</v>
+      </c>
+      <c r="X6" t="n">
         <v>400</v>
-      </c>
-      <c r="X6" t="n">
-        <v>68.37910413871083</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -27840,19 +27840,19 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.13729309820286</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2309599488807</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9482601269169</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>316.3986863185171</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>322.4810740850555</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1177124465037</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>224.8682520946261</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
-        <v>398.0465935392085</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27998,16 +27998,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.517988705216</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>287.2163459097451</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4985557026693</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>88.48881128536601</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28046,16 +28046,16 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>58.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>270.7979644482395</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28071,31 +28071,31 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>294.3826718271959</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.858135136612</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.047816275856</v>
+        <v>175.6474368353909</v>
       </c>
       <c r="J10" t="n">
-        <v>22.13729309820286</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>266.941429538848</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
-        <v>395.9334970102382</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,16 +28116,16 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28223,10 +28223,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>321</v>
@@ -28235,10 +28235,10 @@
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>226.0367322273742</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28274,7 +28274,7 @@
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28286,13 +28286,13 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X12" t="n">
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>321</v>
+        <v>226.0367322273744</v>
       </c>
     </row>
     <row r="13">
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="C15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
@@ -28517,10 +28517,10 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W15" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28712,13 +28712,13 @@
         <v>321</v>
       </c>
       <c r="G18" t="n">
-        <v>18.05909831126195</v>
+        <v>321</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>226.036732227374</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28742,16 +28742,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>321</v>
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>96.3057582470185</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28937,16 +28937,16 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28994,16 +28994,16 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29177,10 +29177,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
         <v>321</v>
@@ -29237,10 +29237,10 @@
         <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29347,10 +29347,10 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29408,16 +29408,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -29426,10 +29426,10 @@
         <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>18.05909831126195</v>
+        <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
@@ -29471,7 +29471,7 @@
         <v>321</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X27" t="n">
         <v>321</v>
@@ -29651,7 +29651,7 @@
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>96.68764642060964</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -29666,7 +29666,7 @@
         <v>321</v>
       </c>
       <c r="I30" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29693,7 +29693,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29933,7 +29933,7 @@
         <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T33" t="n">
         <v>321</v>
@@ -29942,7 +29942,7 @@
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W33" t="n">
         <v>321</v>
@@ -29951,7 +29951,7 @@
         <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34">
@@ -30061,7 +30061,7 @@
         <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30137,7 +30137,7 @@
         <v>321</v>
       </c>
       <c r="H36" t="n">
-        <v>226.0367322273743</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>191.6509141932353</v>
@@ -30170,7 +30170,7 @@
         <v>321</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T36" t="n">
         <v>321</v>
@@ -30179,13 +30179,13 @@
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30295,10 +30295,10 @@
         <v>321</v>
       </c>
       <c r="H38" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I38" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30362,19 +30362,19 @@
         <v>321</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
       </c>
       <c r="H39" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="I39" t="n">
         <v>191.6509141932353</v>
@@ -30416,16 +30416,16 @@
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,19 +30593,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30650,7 +30650,7 @@
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="V42" t="n">
         <v>321</v>
@@ -30659,10 +30659,10 @@
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43">
@@ -30799,10 +30799,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T44" t="n">
         <v>321</v>
@@ -30836,7 +30836,7 @@
         <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
@@ -30848,7 +30848,7 @@
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="I45" t="n">
         <v>191.6509141932353</v>
@@ -30878,25 +30878,25 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>147.4081841180266</v>
+        <v>321</v>
       </c>
       <c r="V45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H2" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I2" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J2" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N2" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O2" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P2" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R2" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S2" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H3" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I3" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J3" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K3" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L3" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M3" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O3" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P3" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R3" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S3" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H4" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I4" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J4" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K4" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L4" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M4" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N4" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O4" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P4" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R4" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S4" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H5" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I5" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J5" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K5" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L5" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N5" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O5" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P5" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R5" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S5" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H6" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I6" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J6" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K6" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L6" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M6" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O6" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P6" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R6" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S6" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H7" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I7" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J7" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K7" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L7" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M7" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N7" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O7" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P7" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R7" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S7" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4100502512562811</v>
       </c>
       <c r="H8" t="n">
-        <v>4.240597989949746</v>
+        <v>4.199427135678389</v>
       </c>
       <c r="I8" t="n">
-        <v>15.96344723618091</v>
+        <v>15.80846231155779</v>
       </c>
       <c r="J8" t="n">
-        <v>35.14370351758794</v>
+        <v>34.80250251256282</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>52.15992964824121</v>
       </c>
       <c r="L8" t="n">
-        <v>65.34340703517589</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
-        <v>72.70713065326633</v>
+        <v>72.00123618090453</v>
       </c>
       <c r="N8" t="n">
-        <v>73.88360804020101</v>
+        <v>73.16629145728643</v>
       </c>
       <c r="O8" t="n">
-        <v>69.76619597989949</v>
+        <v>69.08885427135678</v>
       </c>
       <c r="P8" t="n">
-        <v>59.54383417085427</v>
+        <v>58.96573869346734</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.71493969849246</v>
+        <v>44.28081407035176</v>
       </c>
       <c r="R8" t="n">
-        <v>26.01034673366835</v>
+        <v>25.75781909547739</v>
       </c>
       <c r="S8" t="n">
-        <v>9.435628140703519</v>
+        <v>9.344020100502515</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81259296482412</v>
+        <v>1.794994974874371</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03280402010050248</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2193962264150943</v>
       </c>
       <c r="H9" t="n">
-        <v>2.139679245283019</v>
+        <v>2.118905660377359</v>
       </c>
       <c r="I9" t="n">
-        <v>7.627830188679247</v>
+        <v>7.553773584905661</v>
       </c>
       <c r="J9" t="n">
-        <v>20.93134905660378</v>
+        <v>20.7281320754717</v>
       </c>
       <c r="K9" t="n">
-        <v>35.77500943396227</v>
+        <v>35.42767924528302</v>
       </c>
       <c r="L9" t="n">
-        <v>48.10391509433963</v>
+        <v>47.63688679245283</v>
       </c>
       <c r="M9" t="n">
-        <v>56.13499999999999</v>
+        <v>55.58999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.62072641509435</v>
+        <v>57.06130188679246</v>
       </c>
       <c r="O9" t="n">
-        <v>52.71170754716981</v>
+        <v>52.19994339622642</v>
       </c>
       <c r="P9" t="n">
-        <v>42.3057924528302</v>
+        <v>41.89505660377359</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.28030188679246</v>
+        <v>28.00573584905661</v>
       </c>
       <c r="R9" t="n">
-        <v>13.75535849056604</v>
+        <v>13.62181132075472</v>
       </c>
       <c r="S9" t="n">
-        <v>4.115141509433959</v>
+        <v>4.07518867924528</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.8843207547169808</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01443396226415095</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1839344262295082</v>
       </c>
       <c r="H10" t="n">
-        <v>1.651377049180329</v>
+        <v>1.635344262295083</v>
       </c>
       <c r="I10" t="n">
-        <v>5.585639344262296</v>
+        <v>5.531409836065575</v>
       </c>
       <c r="J10" t="n">
-        <v>13.13165573770492</v>
+        <v>13.00416393442623</v>
       </c>
       <c r="K10" t="n">
-        <v>21.57934426229507</v>
+        <v>21.36983606557376</v>
       </c>
       <c r="L10" t="n">
-        <v>27.61413114754098</v>
+        <v>27.34603278688525</v>
       </c>
       <c r="M10" t="n">
-        <v>29.11522950819672</v>
+        <v>28.83255737704917</v>
       </c>
       <c r="N10" t="n">
-        <v>28.42293442622952</v>
+        <v>28.1469836065574</v>
       </c>
       <c r="O10" t="n">
-        <v>26.25318032786886</v>
+        <v>25.99829508196722</v>
       </c>
       <c r="P10" t="n">
-        <v>22.46413114754097</v>
+        <v>22.24603278688523</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.553</v>
+        <v>15.402</v>
       </c>
       <c r="R10" t="n">
-        <v>8.351442622950817</v>
+        <v>8.270360655737703</v>
       </c>
       <c r="S10" t="n">
-        <v>3.236901639344261</v>
+        <v>3.205475409836064</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.785901639344262</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01003278688524591</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517586</v>
+        <v>248.0502805878618</v>
       </c>
       <c r="M2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>180.6578102564064</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>59.25677413017286</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K3" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L3" t="n">
-        <v>318.4376284546069</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M3" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O3" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P3" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34880,16 +34880,16 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -34901,10 +34901,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>160.9152003049996</v>
+        <v>217.3394793683217</v>
       </c>
       <c r="K4" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.86342193648881</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0517398730831</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -34980,13 +34980,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
-        <v>65.34340703517591</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
@@ -34998,10 +34998,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>59.25677413017286</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>234.1880104510424</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K6" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L6" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M6" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O6" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P6" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
@@ -35126,25 +35126,25 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.952183724144</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>133.058570461152</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>4.06650298976183</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.86342193648881</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>90.02587647980737</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>35.01572123559317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35220,25 +35220,25 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>65.34340703517586</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
+        <v>235.5012052109774</v>
+      </c>
+      <c r="N8" t="n">
         <v>374</v>
       </c>
-      <c r="N8" t="n">
-        <v>181.6174062160025</v>
-      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>59.25677413017286</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>146.1399552942795</v>
+        <v>145.9367383131474</v>
       </c>
       <c r="K9" t="n">
-        <v>226.8788640747536</v>
+        <v>226.5315338860743</v>
       </c>
       <c r="L9" t="n">
-        <v>322.1952904430266</v>
+        <v>321.7282621411399</v>
       </c>
       <c r="M9" t="n">
-        <v>143.0850421645043</v>
+        <v>142.5400421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>192.2472765237492</v>
+        <v>191.6878519954473</v>
       </c>
       <c r="O9" t="n">
-        <v>294.1687294499162</v>
+        <v>293.6569652989728</v>
       </c>
       <c r="P9" t="n">
-        <v>155.9717969674834</v>
+        <v>155.5610611184268</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35357,22 +35357,22 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>8.846453771640441</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4.545391051338223</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,16 +35402,16 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.86342193648881</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L11" t="n">
         <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35475,7 +35475,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>397.8074393630433</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,25 +35691,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
-        <v>17.50927946942293</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>649</v>
       </c>
-      <c r="O14" t="n">
-        <v>162.757678164601</v>
-      </c>
       <c r="P14" t="n">
-        <v>198.5777841804241</v>
+        <v>421.6280856303015</v>
       </c>
       <c r="Q14" t="n">
         <v>592.3686050224903</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>560.5651175276444</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.355038036034114</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>649</v>
@@ -35949,7 +35949,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>223.0503014498772</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O20" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P20" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36405,16 +36405,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L23" t="n">
-        <v>218.2342914572864</v>
+        <v>434.3213551071335</v>
       </c>
       <c r="M23" t="n">
-        <v>40.17514405185721</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36642,16 +36642,16 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>60.29262328527617</v>
+        <v>236.2045428832663</v>
       </c>
       <c r="N26" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36876,22 +36876,22 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>218.2342914572864</v>
+        <v>454.4388343405528</v>
       </c>
       <c r="M29" t="n">
-        <v>4.355038036033999</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
         <v>198.5777841804241</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37116,7 +37116,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L32" t="n">
         <v>649</v>
@@ -37125,7 +37125,7 @@
         <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>59.83165132871924</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L35" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M35" t="n">
         <v>649</v>
       </c>
-      <c r="L35" t="n">
-        <v>649</v>
-      </c>
-      <c r="M35" t="n">
-        <v>341.8698541138008</v>
-      </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O35" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>649</v>
+        <v>236.2045428832663</v>
       </c>
       <c r="N38" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>433.9659648939237</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37827,22 +37827,22 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L41" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>235.7435709267093</v>
       </c>
       <c r="N41" t="n">
-        <v>202.9328222164582</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
         <v>592.3686050224903</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38027,7 +38027,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y43" t="n">
-        <v>33.53464715053765</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="44">
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="N44" t="n">
-        <v>223.0503014498772</v>
+        <v>649</v>
       </c>
       <c r="O44" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
